--- a/Libraries/Vehicle/Linkage/Link5_S2LAC_AU/sm_car_data_Linkage_Link5_S2LAC_AU_NoSteer.xlsx
+++ b/Libraries/Vehicle/Linkage/Link5_S2LAC_AU/sm_car_data_Linkage_Link5_S2LAC_AU_NoSteer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Link5_S2LAC_AU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202936F2-5A98-4529-9E86-3F041B482AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D567D0-C894-4023-8A37-0987EE77D9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30315" yWindow="1515" windowWidth="21600" windowHeight="11295" tabRatio="774" activeTab="3" xr2:uid="{48D06346-6904-4E22-A3AD-44252B9780B0}"/>
+    <workbookView xWindow="915" yWindow="2670" windowWidth="25485" windowHeight="11295" tabRatio="774" xr2:uid="{48D06346-6904-4E22-A3AD-44252B9780B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_Hamba_f" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="58">
   <si>
     <t>Units</t>
   </si>
@@ -201,6 +201,18 @@
   </si>
   <si>
     <t>FiveLinkShockCenterAUNoSteer_Sedan_Hamba_f</t>
+  </si>
+  <si>
+    <t>LowerArmF to Upright</t>
+  </si>
+  <si>
+    <t>LowerArmC to Upright</t>
+  </si>
+  <si>
+    <t>UpperArmR to Upright</t>
+  </si>
+  <si>
+    <t>UpperArmF to Upright</t>
   </si>
 </sst>
 </file>
@@ -334,7 +346,77 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="30">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -793,7 +875,1701 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6">
+        <f>5.80566/2</f>
+        <v>2.9028299999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>2.9028299999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="6">
+        <v>-0.125</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6">
+        <v>-0.125</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <v>2.9028299999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="6">
+        <v>-0.02</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6">
+        <f>5.27788/2</f>
+        <v>2.6389399999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="6">
+        <v>-0.105</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="6">
+        <v>-0.105</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6">
+        <f>5.27788/2</f>
+        <v>2.6389399999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="H20" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="H21" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="21">
+        <v>-0.05</v>
+      </c>
+      <c r="G22" s="21">
+        <v>0.8</v>
+      </c>
+      <c r="H22" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6">
+        <v>5.2778799999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="20">
+        <f>-0.000217+0.05</f>
+        <v>4.9783000000000001E-2</v>
+      </c>
+      <c r="G29" s="20">
+        <v>0.49198500000000001</v>
+      </c>
+      <c r="H29" s="20">
+        <v>0.52585999999999999</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="20">
+        <f>-0.000217+0.05</f>
+        <v>4.9783000000000001E-2</v>
+      </c>
+      <c r="G30" s="20">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="H30" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6">
+        <v>3.6529410000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6">
+        <v>4.3157700000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="18">
+        <v>-0.1</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A29">
+    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A39">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:B34">
+    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:E34">
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33:J34">
+    <cfRule type="cellIs" dxfId="25" priority="8" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40:A42">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FE7FDB-706D-4318-BC3F-DB945174005E}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:P44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6">
+        <f>5.80566/2</f>
+        <v>2.9028299999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <v>2.9028299999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="6">
+        <v>-0.125</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6">
+        <v>-0.125</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <v>2.9028299999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="6">
+        <v>-0.02</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6">
+        <f>5.27788/2</f>
+        <v>2.6389399999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="6">
+        <v>-0.105</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="6">
+        <v>-0.105</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0.68720000000000003</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6">
+        <f>5.27788/2</f>
+        <v>2.6389399999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="H20" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="H21" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="21">
+        <v>0.05</v>
+      </c>
+      <c r="G22" s="21">
+        <v>0.6</v>
+      </c>
+      <c r="H22" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6">
+        <v>5.2778799999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="19">
+        <f>-0.01387-0.04</f>
+        <v>-5.3870000000000001E-2</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0.49195</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0.52285999999999999</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="19">
+        <f>-0.013587-0.04</f>
+        <v>-5.3587000000000003E-2</v>
+      </c>
+      <c r="G30" s="19">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="H30" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6">
+        <v>3.6529410000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6">
+        <v>4.3157700000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="18">
+        <v>-0.1</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A29">
+    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A43">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:B34">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:E34">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33:J34">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBAF9AFE-CCE9-41C5-A10D-81291225854D}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="15" customWidth="1"/>
@@ -847,7 +2623,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -876,13 +2652,13 @@
         <v>11</v>
       </c>
       <c r="F5" s="6">
-        <v>0.22500000000000001</v>
+        <v>0.29913000000000006</v>
       </c>
       <c r="G5" s="6">
-        <v>0.30599999999999999</v>
+        <v>0.44059999999999999</v>
       </c>
       <c r="H5" s="6">
-        <v>0.15</v>
+        <v>0.19097000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -895,13 +2671,13 @@
         <v>11</v>
       </c>
       <c r="F6" s="6">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G6" s="6">
-        <v>0.76600000000000001</v>
+        <v>0.89710000000000001</v>
       </c>
       <c r="H6" s="6">
-        <v>0.15</v>
+        <v>0.18855571428571433</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -916,7 +2692,6 @@
       <c r="F7" s="12"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6">
-        <f>5.80566/2</f>
         <v>2.9028299999999998</v>
       </c>
     </row>
@@ -932,13 +2707,13 @@
         <v>11</v>
       </c>
       <c r="F8" s="6">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="6">
-        <v>0.30599999999999999</v>
+        <v>0.44059999999999999</v>
       </c>
       <c r="H8" s="6">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -954,10 +2729,10 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G9" s="6">
-        <v>0.76600000000000001</v>
+        <v>0.89710000000000001</v>
       </c>
       <c r="H9" s="6">
-        <v>0.15</v>
+        <v>0.18855571428571433</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -987,13 +2762,13 @@
         <v>11</v>
       </c>
       <c r="F11" s="6">
-        <v>-0.125</v>
+        <v>-0.18372714285714289</v>
       </c>
       <c r="G11" s="6">
-        <v>0.30599999999999999</v>
+        <v>0.44059999999999999</v>
       </c>
       <c r="H11" s="6">
-        <v>0.15</v>
+        <v>0.2452914285714286</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1006,13 +2781,13 @@
         <v>11</v>
       </c>
       <c r="F12" s="6">
-        <v>-0.125</v>
+        <v>0.03</v>
       </c>
       <c r="G12" s="6">
-        <v>0.76600000000000001</v>
+        <v>0.89710000000000001</v>
       </c>
       <c r="H12" s="6">
-        <v>0.15</v>
+        <v>0.18855571428571433</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1042,13 +2817,13 @@
         <v>11</v>
       </c>
       <c r="F14" s="6">
-        <v>0.1</v>
+        <v>0.16634428571428575</v>
       </c>
       <c r="G14" s="6">
-        <v>0.45100000000000001</v>
+        <v>0.63060000000000005</v>
       </c>
       <c r="H14" s="6">
-        <v>0.43</v>
+        <v>0.53609214285714291</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1061,13 +2836,14 @@
         <v>11</v>
       </c>
       <c r="F15" s="6">
-        <v>-0.02</v>
+        <f>-0.03</f>
+        <v>-0.03</v>
       </c>
       <c r="G15" s="6">
-        <v>0.68720000000000003</v>
+        <v>0.89280000000000004</v>
       </c>
       <c r="H15" s="6">
-        <v>0.45</v>
+        <v>0.54321428571428576</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1098,13 +2874,13 @@
         <v>11</v>
       </c>
       <c r="F17" s="6">
-        <v>-0.105</v>
+        <v>-0.18372714285714289</v>
       </c>
       <c r="G17" s="6">
-        <v>0.45100000000000001</v>
+        <v>0.63060000000000005</v>
       </c>
       <c r="H17" s="6">
-        <v>0.41</v>
+        <v>0.51255285714285714</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1117,13 +2893,14 @@
         <v>11</v>
       </c>
       <c r="F18" s="6">
-        <v>-0.105</v>
+        <f>-0.07</f>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="G18" s="6">
-        <v>0.68720000000000003</v>
+        <v>0.89280000000000004</v>
       </c>
       <c r="H18" s="6">
-        <v>0.45</v>
+        <v>0.54321428571428576</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1154,13 +2931,13 @@
         <v>11</v>
       </c>
       <c r="F20" s="6">
-        <v>0</v>
+        <v>9.4157142857142894E-3</v>
       </c>
       <c r="G20" s="6">
-        <v>0.73</v>
+        <v>0.89449999999999996</v>
       </c>
       <c r="H20" s="6">
-        <v>0.33</v>
+        <v>0.42648357142857141</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -1175,11 +2952,11 @@
       <c r="F21" s="6">
         <v>0</v>
       </c>
-      <c r="G21" s="23">
-        <v>0.78749999999999998</v>
+      <c r="G21" s="6">
+        <v>0.99209999999999998</v>
       </c>
       <c r="H21" s="6">
-        <v>0.33</v>
+        <v>0.36214285714285716</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -1321,14 +3098,13 @@
         <v>41</v>
       </c>
       <c r="F29" s="20">
-        <f>-0.000217+0.05</f>
-        <v>4.9783000000000001E-2</v>
-      </c>
-      <c r="G29" s="20">
-        <v>0.49198500000000001</v>
-      </c>
-      <c r="H29" s="20">
-        <v>0.52585999999999999</v>
+        <v>-2.6557142857142869E-3</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0.62</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0.65</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>41</v>
@@ -1347,14 +3123,13 @@
         <v>41</v>
       </c>
       <c r="F30" s="20">
-        <f>-0.000217+0.05</f>
-        <v>4.9783000000000001E-2</v>
-      </c>
-      <c r="G30" s="20">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="H30" s="20">
-        <v>0.15</v>
+        <v>5.5166428571428582E-2</v>
+      </c>
+      <c r="G30" s="19">
+        <v>0.85</v>
+      </c>
+      <c r="H30" s="19">
+        <v>0.19</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>41</v>
@@ -1428,7 +3203,7 @@
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
       <c r="H34" s="18">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="J34" s="14" t="s">
         <v>42</v>
@@ -1530,1574 +3305,108 @@
         <v>48</v>
       </c>
     </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A29">
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A40">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+  <conditionalFormatting sqref="A35:A39">
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:B34">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="10" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29:E34">
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33:J34">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FE7FDB-706D-4318-BC3F-DB945174005E}">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:P40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.7109375" style="15" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.04</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6">
-        <f>5.80566/2</f>
-        <v>2.9028299999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
-        <v>2.9028299999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="6">
-        <v>-0.125</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="6">
-        <v>-0.125</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0.76600000000000001</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
-        <v>2.9028299999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0.45100000000000001</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.68720000000000003</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6">
-        <f>5.27788/2</f>
-        <v>2.6389399999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="6">
-        <v>-0.105</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0.45100000000000001</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="6">
-        <v>-0.105</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0.68720000000000003</v>
-      </c>
-      <c r="H18" s="6">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6">
-        <f>5.27788/2</f>
-        <v>2.6389399999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0.73</v>
-      </c>
-      <c r="H20" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="23">
-        <v>0.78749999999999998</v>
-      </c>
-      <c r="H21" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="21">
-        <v>0.05</v>
-      </c>
-      <c r="G22" s="21">
-        <v>0.6</v>
-      </c>
-      <c r="H22" s="21">
-        <v>0.2</v>
-      </c>
-      <c r="J22" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6">
-        <v>5.2778799999999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="19">
-        <f>-0.01387-0.04</f>
-        <v>-5.3870000000000001E-2</v>
-      </c>
-      <c r="G29" s="19">
-        <v>0.49195</v>
-      </c>
-      <c r="H29" s="19">
-        <v>0.52285999999999999</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="19">
-        <f>-0.013587-0.04</f>
-        <v>-5.3587000000000003E-2</v>
-      </c>
-      <c r="G30" s="19">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="H30" s="19">
-        <v>0.15</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6">
-        <v>3.6529410000000002</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6">
-        <v>4.3157700000000006</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="18">
-        <v>-0.1</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A29">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+  <conditionalFormatting sqref="A40:A42">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A40">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+  <conditionalFormatting sqref="A43">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29:B34">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E29:E34">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J33:J34">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBAF9AFE-CCE9-41C5-A10D-81291225854D}">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:P40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.42578125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.29913000000000006</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0.44059999999999999</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0.19097000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0.89710000000000001</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0.18855571428571433</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6">
-        <v>2.9028299999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0.44059999999999999</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.89710000000000001</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.18855571428571433</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
-        <v>2.9028299999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="6">
-        <v>-0.18372714285714289</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0.44059999999999999</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0.2452914285714286</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0.03</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0.89710000000000001</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0.18855571428571433</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
-        <v>2.9028299999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0.16634428571428575</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0.63060000000000005</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0.53609214285714291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="6">
-        <f>-0.03</f>
-        <v>-0.03</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.89280000000000004</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0.54321428571428576</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6">
-        <f>5.27788/2</f>
-        <v>2.6389399999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="6">
-        <v>-0.18372714285714289</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0.63060000000000005</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0.51255285714285714</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="6">
-        <f>-0.07</f>
-        <v>-7.0000000000000007E-2</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0.89280000000000004</v>
-      </c>
-      <c r="H18" s="6">
-        <v>0.54321428571428576</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6">
-        <f>5.27788/2</f>
-        <v>2.6389399999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="6">
-        <v>9.4157142857142894E-3</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0.89449999999999996</v>
-      </c>
-      <c r="H20" s="6">
-        <v>0.42648357142857141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0.99209999999999998</v>
-      </c>
-      <c r="H21" s="6">
-        <v>0.36214285714285716</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="21">
-        <v>-0.05</v>
-      </c>
-      <c r="G22" s="21">
-        <v>0.8</v>
-      </c>
-      <c r="H22" s="21">
-        <v>0.3</v>
-      </c>
-      <c r="J22" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6">
-        <v>5.2778799999999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="20">
-        <v>-2.6557142857142869E-3</v>
-      </c>
-      <c r="G29" s="19">
-        <v>0.62</v>
-      </c>
-      <c r="H29" s="19">
-        <v>0.65</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="20">
-        <v>5.5166428571428582E-2</v>
-      </c>
-      <c r="G30" s="19">
-        <v>0.85</v>
-      </c>
-      <c r="H30" s="19">
-        <v>0.19</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6">
-        <v>3.6529410000000002</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6">
-        <v>4.3157700000000006</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="18">
-        <v>-0.15</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A29">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A40">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A29:B34">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E29:E34">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J33:J34">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+  <conditionalFormatting sqref="A44">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3111,7 +3420,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" style="15" customWidth="1"/>
@@ -3891,29 +4200,103 @@
         <v>48</v>
       </c>
     </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A29">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A40">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="A35:A39">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:B34">
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29:E34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33:J34">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A40:A42">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43:A44">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
